--- a/tests/testthat/fixtures/ex3/tables/irt_poly_all.xlsx
+++ b/tests/testthat/fixtures/ex3/tables/irt_poly_all.xlsx
@@ -214,37 +214,37 @@
     <t xml:space="preserve">step3</t>
   </si>
   <si>
-    <t xml:space="preserve">0.19 (0.062)</t>
+    <t xml:space="preserve">0.19 (0.06)</t>
   </si>
   <si>
     <t xml:space="preserve">-0.19</t>
   </si>
   <si>
-    <t xml:space="preserve">0.75 (0.062)</t>
+    <t xml:space="preserve">0.75 (0.06)</t>
   </si>
   <si>
     <t xml:space="preserve">-0.75</t>
   </si>
   <si>
-    <t xml:space="preserve">0.92 (0.092)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.01 (0.092)</t>
+    <t xml:space="preserve">0.92 (0.09)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.01 (0.09)</t>
   </si>
   <si>
     <t xml:space="preserve">0.09</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39 (0.122)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.03 (0.142)</t>
+    <t xml:space="preserve">1.39 (0.12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.03 (0.14)</t>
   </si>
   <si>
     <t xml:space="preserve">-0.36</t>
   </si>
   <si>
-    <t xml:space="preserve">0.63 (0.12)</t>
+    <t xml:space="preserve">0.63 (0.10)</t>
   </si>
   <si>
     <t xml:space="preserve">-0.63</t>
